--- a/Running_Log_EN.xlsx
+++ b/Running_Log_EN.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emory-my.sharepoint.com/personal/ywu862_emory_edu/Documents/Codex/Video dealing/runningpage/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ywu862\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_64BB6D94B43414B4F6573DFDE83ACF271606E951" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{270B1556-4F64-43CF-9F34-79F4C76ACD6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3330" yWindow="0" windowWidth="21600" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Training Log" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="254">
   <si>
     <t>Running Training Log</t>
   </si>
@@ -1661,10 +1661,18 @@
       <c r="A16" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
+      <c r="B16" s="12">
+        <v>46322</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="14">
+        <v>7.01</v>
+      </c>
+      <c r="E16" s="14">
+        <v>60</v>
+      </c>
       <c r="F16" s="27"/>
       <c r="G16" s="16"/>
       <c r="H16" s="27"/>

--- a/Running_Log_EN.xlsx
+++ b/Running_Log_EN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ywu862\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{270B1556-4F64-43CF-9F34-79F4C76ACD6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EE19005-69A7-492A-969B-A39ED8C4AF24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3330" yWindow="0" windowWidth="21600" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Training Log" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="254">
   <si>
     <t>Running Training Log</t>
   </si>
@@ -1684,10 +1684,18 @@
       <c r="A17" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
+      <c r="B17" s="12">
+        <v>46324</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="14">
+        <v>2</v>
+      </c>
+      <c r="E17" s="14">
+        <v>20</v>
+      </c>
       <c r="F17" s="27"/>
       <c r="G17" s="16"/>
       <c r="H17" s="27"/>
